--- a/server/api/src/main/resources/template/卷王题库导入模板.xlsx
+++ b/server/api/src/main/resources/template/卷王题库导入模板.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29100" windowHeight="14540" activeTab="4"/>
+    <workbookView windowWidth="29100" windowHeight="14640"/>
   </bookViews>
   <sheets>
     <sheet name="单选题" sheetId="1" r:id="rId1"/>
